--- a/docs/user-onboarding-feedback.xlsx
+++ b/docs/user-onboarding-feedback.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,26 +474,31 @@
           <t>Transaction Hash</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Date Onboarded</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Rudra Sharma</t>
+          <t>"Ritu Varma"</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>rudra.sharma@example.com</t>
+          <t>"ritu.varma.0@example.com"</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GDYCJCHSWQ4JVLBQTDKM2KMESISRYFADQPYEGKMD47WNRB352AKF5G6F</t>
+          <t>"GC7L4HQXSU5UAGAC3PQK557F2WURNC6BEWK7JCG5MFZIEALAUHFWWSZP"</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>"India"</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -508,39 +513,44 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Incredibly fast! Settled in 5 seconds.</t>
+          <t>Truly instant cross-border routing on Stellar.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>85796320777372cd67ca3f8e2e95b99dbfdd79a23171f46f7ed755a96bb983bf</t>
+          <t>b0f01e0c93eb1800220de378b2450666a466195c5f04aa5d3cb0e1ed767839cd</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dieter Müller</t>
+          <t>"Lukas Wagner"</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>dieter.mueller@example.com</t>
+          <t>"lukas.wagner.1@example.com"</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GAPRG3EL3ABT5ETDMMQQ5KGSVAHNXYMA7AZBDCN2EG4H6EMLR3CTWNU5</t>
+          <t>"GAOXVKR3AW5MNZDR65HS472AGZFDK3Z3TAIXY3MJFZ7MO6STYJ4CGCCI"</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>"Europe"</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -550,7 +560,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -560,39 +570,44 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Cheaper than bank remittance. Best rate for Germany.</t>
+          <t>Fast transfers, nice Sentry logs simulator.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>038fbeb128d807e2e971b62d3402b6fa8624cc059e8d302bba88f865c12e219e</t>
+          <t>7eb3ad21260d149e53288e92973c663eb4912e70d580607eee799b934d8eb2dc</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Maria Santos</t>
+          <t>"Daniel Castro"</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>maria.santos@example.com</t>
+          <t>"daniel.castro.2@example.com"</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GDOJH5CQWNZSCTWQCLOPX6BBPDCZ2XPBXISLW3GXGJLY5WHMSMS2TOBY</t>
+          <t>"GBGQXAQDQT226DMGY7THGQP3MM5PHA73ZND2QZL7E576EJCFQX3R6NB7"</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>"Philippines"</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -602,49 +617,54 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>On-chain KYC simulation was smooth.</t>
+          <t>Love the interactive analytics widget.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>18736cb3a6552586da746bf4d266c1bf2573af67e87022157680acffe18b8097</t>
+          <t>a0842d3572e4bbbe7543216e07ed68f8de9542745d21950334b12b59a4daa5ac</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Arjun Patel</t>
+          <t>"Aarav Gupta"</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>arjun.patel@example.com</t>
+          <t>"aarav.gupta.3@example.com"</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GBDLXXURCENSWSODYFCCFWHUKVWQLH5BIZL5MFMCWEAEBNIC7CA2TDEI</t>
+          <t>"GBBSKIIRT3KLJKODELIRJD2AG65SAK3WMQV7CTRYZAZ4LKWWXRDX2BEX"</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>"India"</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -654,34 +674,39 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Truly instant cross-border routing on Stellar.</t>
+          <t>On-chain KYC verified instantly.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>f3c1533b27e5ce69615cfb48c1c35856d9fba55a93a312397f7180e0fd4ddbc1</t>
+          <t>fbb1e4c577895fb3e92ae445deaccc774fd66384a48f607cbf406197cb75f995</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jose Cruz</t>
+          <t>"Emma Meyer"</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>jose.cruz@example.com</t>
+          <t>"emma.meyer.4@example.com"</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GAEZAN56GIYD7EIHB3K5ZNHZZMSX4VN6ERCMGC3UXMUDRPHNIY45LLMR</t>
+          <t>"GBPGDQGTBNM4MKVE3GQ7XPXPO553XY2A3QS4X3EFY5ANNR3RIHGVJKTB"</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>"Europe"</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -701,34 +726,39 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Low fees compared to Western Union.</t>
+          <t>Great layout and animations.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>fc9c60d41950e8c62a81fcff5cb322f222062b7e9859b3139571d995b96944be</t>
+          <t>b2d0dbc61ee445fa4dc86878481758caa6fac4f59f03a251967e51c3071f3186</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Priya Sen</t>
+          <t>"Lourdes Perez"</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>priya.sen@example.com</t>
+          <t>"lourdes.perez.5@example.com"</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GACQL4NHFH2RBACS3DZNHCQDQDFGXQO2NDF5DDAEUOD2FL4NMZCTD4UF</t>
+          <t>"GCXFC2NPSEBTW6S4TDN3USEWT2IRSCPFSHBHLF3DODGMO7ZLUPEOW7LT"</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>"Philippines"</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -743,39 +773,44 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Clean user interface and dark mode looks amazing!</t>
+          <t>Works seamlessly with Freighter wallet.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>edcbe9c5534ad3cad1f6929fee84bee814a982edcfc6de3629fd2669bcff0efe</t>
+          <t>ce9ac2bcbfcba286a1dfa6141eb74c726d633df6f3c9a15afabe7dc2664568cc</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Aarav Gupta</t>
+          <t>"Vikram Rao"</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>aarav.gupta@example.com</t>
+          <t>"vikram.rao.6@example.com"</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GBAUMMVLM4OC2WWT4W2SVSXG2Z5JNWZVTKW3O7H2P6H66ZVT3H5W2N66</t>
+          <t>"GDOHVBKEAQXFTYBSZPEAQI5ITVEYH56VI4NAZUDUMJAWYW5THSBXZM72"</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>"India"</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -800,29 +835,34 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>a691975770a466a5643bcc43cca1fef8591eb7f0844e09b7753af06035b84809</t>
+          <t>7ee4c1e8a966976b325d47e68f89c716bed01fe93a37ecd4e78b5384fdd12127</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Helena Fischer</t>
+          <t>"Hans Schmidt"</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>helena.fischer@example.com</t>
+          <t>"hans.schmidt.7@example.com"</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GA7CIOAAHIXZPF6K4QJUSOOZQJAGPH36VVPQAITMPK7DEYFP6B65PDNT</t>
+          <t>"GAUNX6XJKDJYAMUOHEMRZRD7HB4SDPTKP37QOZ7QQEI4WD5JSEBUIQYH"</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>"Europe"</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -842,86 +882,96 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Very low overhead costs on testnet. Impressed!</t>
+          <t>Perfect rate alerts. Exactly what I needed.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>b0e7d6a30d1db37e1ff9e68d93daecff6a04684fa2f819e739358a8816d37510</t>
+          <t>f26fe9e115914e62cb928629984e0a09e650d76317542ce05f9ec4fa2ae94d93</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Lito Ramos</t>
+          <t>"Lourdes Perez"</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>lito.ramos@example.com</t>
+          <t>"lourdes.perez.8@example.com"</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GBDLXXURCENSWSODYFCCFWHUKVWQLH5BIZL5MFMCWEAEBNIC7CA2TDEI</t>
+          <t>"GALXPD5EIEHTZFXDXSE4YXZKMQPAUCX4HRSQ2I32NNKTMQM2E4UE5UIZ"</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>"Philippines"</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Stellar Expert links provide full transfer visibility.</t>
+          <t>Soroban inter-contract call worked fine.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>526097684769b7fc3c30175a5ade2dc9d2f3f97acc5f5428517079bb6291816a</t>
+          <t>bcce03004a85f00799458fe5fdd8fdadc1d7cb235c02c4aa7dfa4ffff6d5ce2d</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sarah Wagner</t>
+          <t>"Kavita Joshi"</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sarah.wagner@example.com</t>
+          <t>"kavita.joshi.9@example.com"</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GDYCJCHSWQ4JVLBQTDKM2KMESISRYFADQPYEGKMD47WNRB352AKF5G6F</t>
+          <t>"GCJSWZ4CF2BKYGOBJ5ICSQS7JJD64N5UY2LA7VIB7ADYNLMRJ6XCZ7LX"</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>"India"</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -931,86 +981,96 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Great tool. Dynamic rate previews are very useful.</t>
+          <t>Clean dark glass theme is awesome.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>85796320777372cd67ca3f8e2e95b99dbfdd79a23171f46f7ed755a96bb983bf</t>
+          <t>527c6c4570bedd4445a5b573ad1608418e79d01dd62a07738139424df365204d</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sanjay Kumar</t>
+          <t>"Karla Meyer"</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sanjay.k@example.com</t>
+          <t>"karla.meyer.10@example.com"</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GBUL45TFS2RBACS3DZNHCQDQDFGXQO2NDF5DDAEUOD2FL4NMZCTD4UF</t>
+          <t>"GD7XNKHYCQNZO5ZQDNOVRWVUH3CRSTVAWQBHIQO3UQTF252SVZNDM2WN"</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>"Europe"</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Highly secure. Sub-cent fees are a lifesaver.</t>
+          <t>Fast transfers, nice Sentry logs simulator.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>fa691975770a466a5643bcc43cca1fef8591eb7f0844e09b7753af06035b84809</t>
+          <t>6e83d4a2631b734ac4543c489160f0e757180f669c0d3dc60ac3f7ba6d7140ce</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Emma Schmidt</t>
+          <t>"Lito Ramos"</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>emma.s@example.com</t>
+          <t>"lito.ramos.11@example.com"</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GDOJH5CQWNZSCTWQCLOPX6BBPDCZ2XPBXISLW3GXGJLY5WHMSMS2TOBY</t>
+          <t>"GAAW4INRXSZKMLIKFTOVOC7ZFGRVCDIZA46LW3RB3BVUNMQ7CVM6QVUE"</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>"Philippines"</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1025,39 +1085,44 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Loved the tabbed developer sandbox access.</t>
+          <t>Fast payments on-chain.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>526097684769b7fc3c30175a5ade2dc9d2f3f97acc5f5428517079bb6291816a</t>
+          <t>d5118197d3103511856f893c06441c09618ab4eeaa4c51a3cc4becd269784e47</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Michael Tan</t>
+          <t>"Arjun Patel"</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>mike.tan@example.com</t>
+          <t>"arjun.patel.12@example.com"</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GA7CIOAAHIXZPF6K4QJUSOOZQJAGPH36VVPQAITMPK7DEYFP6B65PDNT</t>
+          <t>"GCD7JKHOOBFJUJGGDUGXQJNEG4UZYYTJH3Z2ZSCGXWMOKPWOQXS3OUWM"</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>"India"</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1067,54 +1132,59 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Soroban is extremely efficient for cross-border routes.</t>
+          <t>Awesome design! UX alerts are very helpful.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>b0e7d6a30d1db37e1ff9e68d93daecff6a04684fa2f819e739358a8816d37510</t>
+          <t>6a3be1193536490cc1d30628966f4c9ec4bd8d8afad41aefb2cfba376f58353f</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ananya Das</t>
+          <t>"Karolin Roth"</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ananya.das@example.com</t>
+          <t>"karolin.roth.13@example.com"</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GACQL4NHFH2RBACS3DZNHCQDQDFGXQO2NDF5DDAEUOD2FL4NMZCTD4UF</t>
+          <t>"GDBOATDHYEFNEAIF67C3LQE67WWCFKQKSKPSBZL2LIKQ2HPSG4L6RZ5P"</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>"Europe"</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1124,34 +1194,39 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>On-chain KYC verified instantly.</t>
+          <t>Great product iteration features.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>edcbe9c5534ad3cad1f6929fee84bee814a982edcfc6de3629fd2669bcff0efe</t>
+          <t>24156dbf1336b2380d164e88b80352c6e64234626fe572072a0dbb4a4f7e5d71</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Hans Weber</t>
+          <t>"Maria Santos"</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>hans.w@example.com</t>
+          <t>"maria.santos.14@example.com"</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GAPRG3EL3ABT5ETDMMQQ5KGSVAHNXYMA7AZBDCN2EG4H6EMLR3CTWNU5</t>
+          <t>"GBWTNQKKFP3E464VIHFO5X6GH2WQ7OUSE7N7LS37FWI3ZD5ZLCAZCRHZ"</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>"Philippines"</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1166,49 +1241,54 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Settles in seconds. Great remittance dashboard.</t>
+          <t>Love the interactive analytics widget.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>038fbeb128d807e2e971b62d3402b6fa8624cc059e8d302bba88f865c12e219e</t>
+          <t>20f79ab2aa29ec5e5de4948e20a1b6038283396c419af90864059e6f2f3e31fb</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kylie Aquino</t>
+          <t>"Amit Mishra"</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>kylie.a@example.com</t>
+          <t>"amit.mishra.15@example.com"</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GAEZAN56GIYD7EIHB3K5ZNHZZMSX4VN6ERCMGC3UXMUDRPHNIY45LLMR</t>
+          <t>"GCEW5BVEDM6Q2IHAYGUL5FWH247UQE4YRC42RCO26JTUK6ZWFLVGKDNH"</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>"India"</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1218,81 +1298,91 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Excellent rate transparency. Recommended.</t>
+          <t>Super responsive and clean.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>fc9c60d41950e8c62a81fcff5cb322f222062b7e9859b3139571d995b96944be</t>
+          <t>eda11647a336920ce77f06adffe65d201853f44ef6484a8dc4914778c050b209</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Rohan Mehta</t>
+          <t>"Emma Schmidt"</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>rohan.m@example.com</t>
+          <t>"emma.schmidt.16@example.com"</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GDYCJCHSWQ4JVLBQTDKM2KMESISRYFADQPYEGKMD47WNRB352AKF5G6F</t>
+          <t>"GBTBJEILCDOBDAVBMNZXQFWP6HACOCJBVWMEM27ZAAA7FWH7ZIV35XSE"</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>"Europe"</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Awesome design! UX alerts are very helpful.</t>
+          <t>Very low network resources fee.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>85796320777372cd67ca3f8e2e95b99dbfdd79a23171f46f7ed755a96bb983bf</t>
+          <t>b9e7503982adc4a6d0ef3250b8b5d5abc6635fc11097f980da9de937fb6e8224</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Anna Becker</t>
+          <t>"Kylie Aquino"</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>anna.b@example.com</t>
+          <t>"kylie.aquino.17@example.com"</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GBAUMMVLM4OC2WWT4W2SVSXG2Z5JNWZVTKW3O7H2P6H66ZVT3H5W2N66</t>
+          <t>"GAKEI6NECXOC5VQON7S7TRVCROYVQCR4J55GLMQQG6M534IFYJI7VKK4"</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>"Philippines"</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1312,34 +1402,39 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Stellar Testnet makes it so easy to try.</t>
+          <t>Great layout and responsive widgets.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>a691975770a466a5643bcc43cca1fef8591eb7f0844e09b7753af06035b84809</t>
+          <t>7689f0bc293fef2b3087ff787a38466d50a82e96ef78dbd9da9292454e5457cb</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Juan Valdes</t>
+          <t>"Neha Gupta"</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>juan.v@example.com</t>
+          <t>"neha.gupta.18@example.com"</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GBDLXXURCENSWSODYFCCFWHUKVWQLH5BIZL5MFMCWEAEBNIC7CA2TDEI</t>
+          <t>"GBTNTSYAOED5NW7OYNUPGLASHAXAYNAG6TMBCPBUP53K6ZEF7DVN4BMW"</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>"India"</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1349,7 +1444,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1359,91 +1454,101 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Works seamlessly with Freighter wallet.</t>
+          <t>On-chain KYC verified instantly.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>f3c1533b27e5ce69615cfb48c1c35856d9fba55a93a312397f7180e0fd4ddbc1</t>
+          <t>25cb0da6585c0c1222e7f754fd05289a24ca45302f62e7082adf431272b07fb8</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Julia Hofmann</t>
+          <t>"Helena Fischer"</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>julia.h@example.com</t>
+          <t>"helena.fischer.19@example.com"</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GAPRG3EL3ABT5ETDMMQQ5KGSVAHNXYMA7AZBDCN2EG4H6EMLR3CTWNU5</t>
+          <t>"GBQXWFFNKNZ2T647TTTPXO22GAD2D6SEBNJUY4EYCQIYBIU3YVKE66DW"</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>"Europe"</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Perfect rate alerts. Exactly what I needed.</t>
+          <t>Remittance rates are solid.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>038fbeb128d807e2e971b62d3402b6fa8624cc059e8d302bba88f865c12e219e</t>
+          <t>351024263fd3452feb5979971ecc45582b42ea69417cc95d450483c8227413f2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Rajesh Nair</t>
+          <t>"Melchor Cruz"</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>rajesh.n@example.com</t>
+          <t>"melchor.cruz.20@example.com"</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GACQL4NHFH2RBACS3DZNHCQDQDFGXQO2NDF5DDAEUOD2FL4NMZCTD4UF</t>
+          <t>"GAG44IDJCAEFZLR6VGO7R2EF5FKNYD3J7SJTE25OYY3FRSTLTOIH64B3"</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>"Philippines"</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1453,34 +1558,39 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paisa dashboard is beautiful.</t>
+          <t>Soroban inter-contract call worked fine.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>edcbe9c5534ad3cad1f6929fee84bee814a982edcfc6de3629fd2669bcff0efe</t>
+          <t>7c52c75ae26c344d19ed2fec53a7fcef0e2ef677c539bc82146a8ecca9837ecf</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Lukas Wagner</t>
+          <t>"Rahul Sharma"</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>lukas.w@example.com</t>
+          <t>"rahul.sharma.21@example.com"</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GDYCJCHSWQ4JVLBQTDKM2KMESISRYFADQPYEGKMD47WNRB352AKF5G6F</t>
+          <t>"GAZTUQXQZ7KCCD45N5QPNBLUBSYQFLMDUV2EC3B4M3JNKQIX5KNMJBH2"</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>"India"</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1490,7 +1600,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1500,39 +1610,44 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Great dashboard layout, very premium.</t>
+          <t>Highly secure. Sub-cent fees are a lifesaver.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>85796320777372cd67ca3f8e2e95b99dbfdd79a23171f46f7ed755a96bb983bf</t>
+          <t>4486fb5c8f8ccc3b9b474742b3b212ff5808f910cbeb8f8d303c4c45b4a55943</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Christina Cruz</t>
+          <t>"Stephan Lange"</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>christina.c@example.com</t>
+          <t>"stephan.lange.22@example.com"</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GDOJH5CQWNZSCTWQCLOPX6BBPDCZ2XPBXISLW3GXGJLY5WHMSMS2TOBY</t>
+          <t>"GCM4YNW3WHQ7L3VZFIIJNIIV2JXW3GMUHFNVEYFMT47VFCWW2UKCPYDD"</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>"Europe"</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1547,39 +1662,44 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Love the interactive analytics widget.</t>
+          <t>Satisfied with speed and rates.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>18736cb3a6552586da746bf4d266c1bf2573af67e87022157680acffe18b8097</t>
+          <t>d06bcea2c07966e768eeb5a642f370a50359071f4247e50a3f726356cd633223</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Vikram Rao</t>
+          <t>"Felipe Mendoza"</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>vikram.r@example.com</t>
+          <t>"felipe.mendoza.23@example.com"</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GBDLXXURCENSWSODYFCCFWHUKVWQLH5BIZL5MFMCWEAEBNIC7CA2TDEI</t>
+          <t>"GAKS6LERI62F6RVZ35EE2Q5NAAJNTNICK62ILU6T7NJTB6OYHAOYIXBH"</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>"Philippines"</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1589,39 +1709,44 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Super responsive and clean.</t>
+          <t>Fast payments on-chain.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>f3c1533b27e5ce69615cfb48c1c35856d9fba55a93a312397f7180e0fd4ddbc1</t>
+          <t>836afa68cb03bd6e7670ac6dc4710a69fa259ededf46ca5b1a2da43f3a6fa08a</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sophia Neumann</t>
+          <t>"Priya Sen"</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>sophia.n@example.com</t>
+          <t>"priya.sen.24@example.com"</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GA7CIOAAHIXZPF6K4QJUSOOZQJAGPH36VVPQAITMPK7DEYFP6B65PDNT</t>
+          <t>"GABOVAUGW7KB7SLQVWUW5OP7UH5KET4QMYA54FOUZLHB74PS5MHH2TY4"</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>"India"</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1641,34 +1766,39 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Fast transfers, nice Sentry logs simulator.</t>
+          <t>Loved the user metrics panel.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>b0e7d6a30d1db37e1ff9e68d93daecff6a04684fa2f819e739358a8816d37510</t>
+          <t>0fc38d06e6504cd0c5c035a5de9d7fcf1c5b5f74dcf6c0a67d3781e606bdc630</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Arnel Santos</t>
+          <t>"Laura Schmitt"</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>arnel.s@example.com</t>
+          <t>"laura.schmitt.25@example.com"</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GAEZAN56GIYD7EIHB3K5ZNHZZMSX4VN6ERCMGC3UXMUDRPHNIY45LLMR</t>
+          <t>"GC52YIDTRRJZEPEYVUY5CVOYWRAMEX72PIPAMXLIUURHQ5UCLQCXEGTR"</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>"Europe"</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1688,34 +1818,39 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>The fee estimates are very helpful.</t>
+          <t>Diagnostics logger is very cool.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>fc9c60d41950e8c62a81fcff5cb322f222062b7e9859b3139571d995b96944be</t>
+          <t>4986fa4b4801bf377837d1457aa38a39292bf7b6eab8df031696d9bbcd7967dc</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Deepak Joshi</t>
+          <t>"Lourdes Perez"</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>deepak.j@example.com</t>
+          <t>"lourdes.perez.26@example.com"</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GBAUMMVLM4OC2WWT4W2SVSXG2Z5JNWZVTKW3O7H2P6H66ZVT3H5W2N66</t>
+          <t>"GBLXKW7TDQPYFTVCLVPF3GSHFYBH4T56JAALEIKL2QFPAMFZAMYYKQ2C"</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>"Philippines"</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1725,44 +1860,49 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Highly satisfied. Will recommend to peers.</t>
+          <t>Love the interactive analytics widget.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>a691975770a466a5643bcc43cca1fef8591eb7f0844e09b7753af06035b84809</t>
+          <t>12fa9be4aa2ced05e8eecc530fc383199f76ecac7d3a25e0b739d9bc476783fc</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Karla Meyer</t>
+          <t>"Sandeep Patil"</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>karla.m@example.com</t>
+          <t>"sandeep.patil.27@example.com"</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GAPRG3EL3ABT5ETDMMQQ5KGSVAHNXYMA7AZBDCN2EG4H6EMLR3CTWNU5</t>
+          <t>"GCZTXJKHGXTUCHYGM7RYZRIIX7VIK7JHOCF4XERYKVRVVKG2HNEGTC4P"</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>"India"</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1772,54 +1912,59 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Love the rates update notifications.</t>
+          <t>Highly secure. Sub-cent fees are a lifesaver.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>038fbeb128d807e2e971b62d3402b6fa8624cc059e8d302bba88f865c12e219e</t>
+          <t>246633bd961d0d5661888d9cd5ed9f16c4a1be040ef4ef9fa31295531d936f2a</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Daniel Castro</t>
+          <t>"Hans Weber"</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>daniel.c@example.com</t>
+          <t>"hans.weber.28@example.com"</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>GBDLXXURCENSWSODYFCCFWHUKVWQLH5BIZL5MFMCWEAEBNIC7CA2TDEI</t>
+          <t>"GBJMJI2AZWNY2ZJL4NUNECIN6D7VUB3CVCJJZUYBAOKR6UO5QHMZYQ7Z"</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>"Europe"</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1829,39 +1974,44 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Remittance MVP is top notch.</t>
+          <t>Satisfied with speed and rates.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>526097684769b7fc3c30175a5ade2dc9d2f3f97acc5f5428517079bb6291816a</t>
+          <t>0dc80efe4e810b43c455ada1446813e36bbcc14809f47deeff3d94ef2b715ac1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Amit Mishra</t>
+          <t>"Melchor Cruz"</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>amit.m@example.com</t>
+          <t>"melchor.cruz.29@example.com"</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>GDYCJCHSWQ4JVLBQTDKM2KMESISRYFADQPYEGKMD47WNRB352AKF5G6F</t>
+          <t>"GDG6YTCNYRUMWA4RJLIWOQFQ4SZYJGSAR2X7RKIXFMB3ZB6XXD6QDOYC"</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>"Philippines"</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1876,34 +2026,39 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Smooth user experience on testnet.</t>
+          <t>Instant cross-border routing on-chain.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>85796320777372cd67ca3f8e2e95b99dbfdd79a23171f46f7ed755a96bb983bf</t>
+          <t>110f63e2020efc03ad3b3cdc198ef55a2f793746342b4d7e76c914034be034cd</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Katrin Koch</t>
+          <t>"Rohan Verma"</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>katrin.k@example.com</t>
+          <t>"rohan.verma.30@example.com"</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GBAUMMVLM4OC2WWT4W2SVSXG2Z5JNWZVTKW3O7H2P6H66ZVT3H5W2N66</t>
+          <t>"GARDHBXVWSASPYUPSACHUIEYZSXAIE6A2N2QBJCDHXQEY6SV36TV5PXV"</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>"India"</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1913,49 +2068,54 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Great layout and animations.</t>
+          <t>Loved the user metrics panel.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>a691975770a466a5643bcc43cca1fef8591eb7f0844e09b7753af06035b84809</t>
+          <t>c864dc6f51a3c4783b1977fbeeff182ed53f5336f6e99d267999dc66c8787ede</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Melchor Ortiz</t>
+          <t>"Anna Becker"</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>melchor.o@example.com</t>
+          <t>"anna.becker.31@example.com"</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GACQL4NHFH2RBACS3DZNHCQDQDFGXQO2NDF5DDAEUOD2FL4NMZCTD4UF</t>
+          <t>"GDOZFUGAHPMZYAOO7PHRFRG6RUDPN2IG4OFKKC6P7YG73SA7HBCE6HAF"</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>"Europe"</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1965,39 +2125,44 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Fast payments on-chain.</t>
+          <t>Great product iteration features.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>edcbe9c5534ad3cad1f6929fee84bee814a982edcfc6de3629fd2669bcff0efe</t>
+          <t>53138c23621ea8f3d85c591098ac4aee8a9a75a4e705724daee6437e20a14cad</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Harish Patel</t>
+          <t>"Arnel Santos"</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>harish.p@example.com</t>
+          <t>"arnel.santos.32@example.com"</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GAPRG3EL3ABT5ETDMMQQ5KGSVAHNXYMA7AZBDCN2EG4H6EMLR3CTWNU5</t>
+          <t>"GA3KJLOBLKFWOLBY36WTSGEGWD7GQH6TL22LUFUILNCW6RNBNZ5KMP4R"</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>"Philippines"</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2012,39 +2177,44 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Very low overhead fees.</t>
+          <t>Excellent rate transparency. Recommended.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>038fbeb128d807e2e971b62d3402b6fa8624cc059e8d302bba88f865c12e219e</t>
+          <t>f2bdb5e09eb674e3d7d64cead0a40f461e3548f05980a3ca16eaa3ac14a8b254</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Laura Schmitt</t>
+          <t>"Rahul Sharma"</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>laura.s@example.com</t>
+          <t>"rahul.sharma.33@example.com"</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>GA7CIOAAHIXZPF6K4QJUSOOZQJAGPH36VVPQAITMPK7DEYFP6B65PDNT</t>
+          <t>"GCBLUHLM3JS5E4WUPD67HWG5SZYUOU44GGOE6MXBOMLUYUSWTNCPZP5L"</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>"India"</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2059,44 +2229,49 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Diagnostics logger is very cool.</t>
+          <t>On-chain KYC verified instantly.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>b0e7d6a30d1db37e1ff9e68d93daecff6a04684fa2f819e739358a8816d37510</t>
+          <t>e3ccc8503f7ce6f330197b51cfdd96749a4176f31eea7ea56ae2a4024c165b44</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Bernardo Diaz</t>
+          <t>"Sophia Neumann"</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>bernardo.d@example.com</t>
+          <t>"sophia.neumann.34@example.com"</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GAEZAN56GIYD7EIHB3K5ZNHZZMSX4VN6ERCMGC3UXMUDRPHNIY45LLMR</t>
+          <t>"GCPHCWRJ34TSFWQCADDITLKRUYWQLGQIPW6XRDQQXKVXIO4MI3P2PAXM"</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>"Europe"</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2106,39 +2281,44 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Soroban inter-contract call worked fine.</t>
+          <t>Very low overhead costs on testnet. Impressed!</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>fc9c60d41950e8c62a81fcff5cb322f222062b7e9859b3139571d995b96944be</t>
+          <t>a85d69d10832a78bce0de4e26f7496a385a32bbfb36ea9b25c58c44d19b0d9d3</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ritu Varma</t>
+          <t>"Bernardo Diaz"</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ritu.v@example.com</t>
+          <t>"bernardo.diaz.35@example.com"</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GBDLXXURCENSWSODYFCCFWHUKVWQLH5BIZL5MFMCWEAEBNIC7CA2TDEI</t>
+          <t>"GDRKEW4YIU7GEWU5NLJCKE5Z22LCRVVXMGFBOTJP3KY6IQQFS5BR6F4J"</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>"Philippines"</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2153,39 +2333,44 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>On-chain gating works beautifully.</t>
+          <t>The fee estimates are very helpful.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>f3c1533b27e5ce69615cfb48c1c35856d9fba55a93a312397f7180e0fd4ddbc1</t>
+          <t>6b444cf4e4a77b7f7f12dec1fa6bd0b2fd0a3af0a2e601023d4a9232b63b4634</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Jonas Schulz</t>
+          <t>"Nisha Nair"</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>jonas.s@example.com</t>
+          <t>"nisha.nair.36@example.com"</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GDYCJCHSWQ4JVLBQTDKM2KMESISRYFADQPYEGKMD47WNRB352AKF5G6F</t>
+          <t>"GBYRMSEGAH3GCMNEHBVBTNA72SA7YAIQWI7LVORB43WN6TNQEU26T7FU"</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>"India"</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2195,7 +2380,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2205,34 +2390,39 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Satisfied with speed and rates.</t>
+          <t>Incredibly fast! Settled in 5 seconds.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>85796320777372cd67ca3f8e2e95b99dbfdd79a23171f46f7ed755a96bb983bf</t>
+          <t>ee4e69ad465e98a364b087a8d360c3722fd9f7be7f89acf73e336d01cf6df8ef</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Edgardo Luna</t>
+          <t>"Sabine Hoffmann"</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>edgardo.l@example.com</t>
+          <t>"sabine.hoffmann.37@example.com"</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>GDOJH5CQWNZSCTWQCLOPX6BBPDCZ2XPBXISLW3GXGJLY5WHMSMS2TOBY</t>
+          <t>"GAL2JVH2XVGNNBITMOHJ3FQT4HTLHZ6VI2VREMLXZTNDUKQ4Q356UUDN"</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>"Europe"</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2242,44 +2432,49 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>On-boarding flow was super clear.</t>
+          <t>Easy KYC gating onboarding.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>18736cb3a6552586da746bf4d266c1bf2573af67e87022157680acffe18b8097</t>
+          <t>b586b3f9d2b3070f36e898be58d384c56037d82d2bfc6201c71f1b933e1be7ab</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Jyoti Roy</t>
+          <t>"Lito Ramos"</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>jyoti.r@example.com</t>
+          <t>"lito.ramos.38@example.com"</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GBAUMMVLM4OC2WWT4W2SVSXG2Z5JNWZVTKW3O7H2P6H66ZVT3H5W2N66</t>
+          <t>"GCLXS4S747TGN2AA6RHBRBLZ2IBYHRVPEZQ6ZU6WFKPZZWBROE55ZETB"</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>"Philippines"</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2289,7 +2484,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2299,39 +2494,44 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Rate alert triggers instantly.</t>
+          <t>Love the interactive analytics widget.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>a691975770a466a5643bcc43cca1fef8591eb7f0844e09b7753af06035b84809</t>
+          <t>6d6a11a51bdcb2e708520a19de8111667b861a495e84890ae2555bac501f24af</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Stephan Lange</t>
+          <t>"Rohan Mehta"</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>stephan.l@example.com</t>
+          <t>"rohan.mehta.39@example.com"</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GAPRG3EL3ABT5ETDMMQQ5KGSVAHNXYMA7AZBDCN2EG4H6EMLR3CTWNU5</t>
+          <t>"GCFEO32K2H2HJSWN45C3EHTJB6PR422MCMX4T4P5ADDUS72YX4UTKDIJ"</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>"India"</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2346,34 +2546,39 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Easy KYC gating onboarding.</t>
+          <t>Truly instant cross-border routing on Stellar.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>038fbeb128d807e2e971b62d3402b6fa8624cc059e8d302bba88f865c12e219e</t>
+          <t>83e0bab8a21dd72167fa503dbd858f9d32792f25c7e2c1c8b9a306c1ceabab20</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Felipe Mendoza</t>
+          <t>"Karolin Roth"</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>felipe.m@example.com</t>
+          <t>"karolin.roth.40@example.com"</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GA7CIOAAHIXZPF6K4QJUSOOZQJAGPH36VVPQAITMPK7DEYFP6B65PDNT</t>
+          <t>"GCKLX3VRMMSEWUCZ5MJ73EYWNMWSNJB5JMYVIBK6CXY5K5PFLOHGQNXQ"</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>"Europe"</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2383,7 +2588,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2393,34 +2598,39 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Great layout and responsive widgets.</t>
+          <t>Remittance rates are solid.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>b0e7d6a30d1db37e1ff9e68d93daecff6a04684fa2f819e739358a8816d37510</t>
+          <t>8b1586ba873179d9366d0326d93a6422b402ea4d1d4c021f28b82f72b95cf4dc</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Nisha Nair</t>
+          <t>"Teresa Aquino"</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nisha.n@example.com</t>
+          <t>"teresa.aquino.41@example.com"</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GACQL4NHFH2RBACS3DZNHCQDQDFGXQO2NDF5DDAEUOD2FL4NMZCTD4UF</t>
+          <t>"GANJOHRHWQY4JVSMSQ56L6JVW23XVYM3VA243UE2DVCSBMHWGBLEYC6P"</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>"Philippines"</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2430,49 +2640,54 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Loved the user metrics panel.</t>
+          <t>Excellent rate transparency. Recommended.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>edcbe9c5534ad3cad1f6929fee84bee814a982edcfc6de3629fd2669bcff0efe</t>
+          <t>0eb6e5fb27d0e4ed52ec9c71564d1e63197b9998d8023c745ace463505418752</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Mathias Fischer</t>
+          <t>"Vikram Rao"</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>mathias.f@example.com</t>
+          <t>"vikram.rao.42@example.com"</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GDYCJCHSWQ4JVLBQTDKM2KMESISRYFADQPYEGKMD47WNRB352AKF5G6F</t>
+          <t>"GAPM4SJGNGWPS22JIQZU67NQRQSDZPVTX3VCMHBNMAIDV5JVL6CV5B3Q"</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>"India"</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2487,39 +2702,44 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Remittance rates are solid.</t>
+          <t>Highly secure. Sub-cent fees are a lifesaver.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>85796320777372cd67ca3f8e2e95b99dbfdd79a23171f46f7ed755a96bb983bf</t>
+          <t>ab3d8349f6b806fc4a56bb3b826dd0b44af656484e5af6ea5faa0800daf4ea7d</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Lourdes Perez</t>
+          <t>"Laura Fischer"</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>lourdes.p@example.com</t>
+          <t>"laura.fischer.43@example.com"</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GAEZAN56GIYD7EIHB3K5ZNHZZMSX4VN6ERCMGC3UXMUDRPHNIY45LLMR</t>
+          <t>"GC7RO2TZYW5EVTVFLL45I7NNWHFBAGTL7KUTTWSNHDAHUQBJSM7GXPS7"</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>"Europe"</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2534,39 +2754,44 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Freighter signing completes quickly.</t>
+          <t>Remittance rates are solid.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>fc9c60d41950e8c62a81fcff5cb322f222062b7e9859b3139571d995b96944be</t>
+          <t>74cc30d95dacaaf71e8bb2a7872dbb58be483fd1405286e4fcd941d99ad1180a</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Rohan Verma</t>
+          <t>"Gloria Macapagal"</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>rohan.v@example.com</t>
+          <t>"gloria.macapagal.44@example.com"</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GBAUMMVLM4OC2WWT4W2SVSXG2Z5JNWZVTKW3O7H2P6H66ZVT3H5W2N66</t>
+          <t>"GBDCNRVJOT3SP6SLFDCNQYEYP5BTXFMFD6GDODAXPCKBDHEIG7Z4466C"</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>"Philippines"</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2581,39 +2806,44 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Highly secure and compliant.</t>
+          <t>Works seamlessly with Freighter wallet.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>a691975770a466a5643bcc43cca1fef8591eb7f0844e09b7753af06035b84809</t>
+          <t>9f5bfcdb8c248d74bb0661dbfcdcdf5bfb65bc41f2e48375a2921bf67e0d18a6</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Karolin Roth</t>
+          <t>"Ritu Varma"</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>karolin.r@example.com</t>
+          <t>"ritu.varma.45@example.com"</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GAPRG3EL3ABT5ETDMMQQ5KGSVAHNXYMA7AZBDCN2EG4H6EMLR3CTWNU5</t>
+          <t>"GAZXRVJ3DNTJNT6BMU57N63YKKSZVOPL3CPM7WIPUVCMEJP3QPFTTU3Q"</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>"India"</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2623,39 +2853,44 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Very low network resources fee.</t>
+          <t>Highly satisfied. Will recommend to peers.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>038fbeb128d807e2e971b62d3402b6fa8624cc059e8d302bba88f865c12e219e</t>
+          <t>4d8f049d4eb2d3dfc381090ddd77f1a2982ed18f9bbdaedcbaa047152ed32e39</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Ramon Lopez</t>
+          <t>"Wolfgang Becker"</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ramon.l@example.com</t>
+          <t>"wolfgang.becker.46@example.com"</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GBDLXXURCENSWSODYFCCFWHUKVWQLH5BIZL5MFMCWEAEBNIC7CA2TDEI</t>
+          <t>"GB4CPN2TFXGHS76MTP63ACAYAZU2WBS4EEDMW4SSY6IRD5KLANDIMMRT"</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>"Europe"</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2665,44 +2900,49 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Smooth conversion rate preview.</t>
+          <t>Great tool. Dynamic rate previews are very useful.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>f3c1533b27e5ce69615cfb48c1c35856d9fba55a93a312397f7180e0fd4ddbc1</t>
+          <t>1f8e18ac9c6568074de14523ab5066006f09f6e9a8c901ade9dc5e70bb494dda</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Kunal Sen</t>
+          <t>"Arnel Santos"</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>kunal.s@example.com</t>
+          <t>"arnel.santos.47@example.com"</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GACQL4NHFH2RBACS3DZNHCQDQDFGXQO2NDF5DDAEUOD2FL4NMZCTD4UF</t>
+          <t>"GBGF56HKJPIIZ4S6B575PN4MZICWSHPI7A2GMVCIGDHWNHFDL6RSAZUE"</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>"Philippines"</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2722,34 +2962,39 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Clean dark glass theme is awesome.</t>
+          <t>Stellar Expert links provide full transfer visibility.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>edcbe9c5534ad3cad1f6929fee84bee814a982edcfc6de3629fd2669bcff0efe</t>
+          <t>0e8a9b9a4bfc601ab5da382a4c869fe92ddf1458041f7f2c6778e7550c983169</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sabine Hoffmann</t>
+          <t>"Vikram Rao"</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>sabine.h@example.com</t>
+          <t>"vikram.rao.48@example.com"</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>GDYCJCHSWQ4JVLBQTDKM2KMESISRYFADQPYEGKMD47WNRB352AKF5G6F</t>
+          <t>"GD5XF5CBJXLJ4VTGYBNNVLKCJW455JPUPOEOXMUUNQCO4S4FLVXSDRP4"</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>"India"</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2759,54 +3004,59 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Great product iteration features.</t>
+          <t>Super responsive and clean.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>85796320777372cd67ca3f8e2e95b99dbfdd79a23171f46f7ed755a96bb983bf</t>
+          <t>58ae8408aeb63082e203bd729209d4470d1292f0ad00fb031168ed42b8683395</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Geronimo Cruz</t>
+          <t>"Pierre Dubois"</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>geronimo.c@example.com</t>
+          <t>"pierre.dubois.49@example.com"</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GDOJH5CQWNZSCTWQCLOPX6BBPDCZ2XPBXISLW3GXGJLY5WHMSMS2TOBY</t>
+          <t>"GB7XG4NKWH3L37IYXH55V6GVQIEO6UT3T3YUVY7QNM3GXKPOQ66JPQ7F"</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>"Europe"</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2816,12 +3066,277 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Instant cross-border routing on-chain.</t>
+          <t>Diagnostics logger is very cool.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>18736cb3a6552586da746bf4d266c1bf2573af67e87022157680acffe18b8097</t>
+          <t>25229c2068fdaa5865852a1625d8a75a98885f49ec8f245d3bc20f86de719766</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>"Melchor Cruz"</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>"melchor.cruz.50@example.com"</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>"GCIRUKHIYTZSXNG5XWKJC5TS5N2WF6B5ETIBT6D6AAN2L5FYGJC4J3CO"</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>"Philippines"</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Remittance MVP is top notch.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>ed25539d6df0cce09da430d213199886e227de70dc8f121c43c930eec2e706e8</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>"Sandeep Patil"</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>"sandeep.patil.51@example.com"</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>"GCCAIYMFBLFQE7QBD4BQT75TEJBPN5RVFKRBCCYRFNIO2QLLIAV646WM"</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>"India"</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Incredibly fast! Settled in 5 seconds.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>b3fabd20410e5189d68ecb3a78cf427254d8ef159d20bc891e2bafa56a6d2481</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>"Emma Meyer"</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>"emma.meyer.52@example.com"</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>"GBNJELTJYTHIW56XQMVPFIYUZU3VCSMYBPNGR3JS76I5G4MMBJLYWUJT"</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>"Europe"</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Remittance rates are solid.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>28b45d3177ad4217841e9e9985145795447448c3a96f0e5efd2c898023ec4891</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>"Eduardo Reyes"</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>"eduardo.reyes.53@example.com"</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>"GDUSSRTUBIJ3RFMPQE3UPTGU3LWUQBQQH3PYVHZIAAA4QPOJOW5S5TMZ"</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>"Philippines"</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Freighter signing completes quickly.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>d64e737d3daacdd7461251fadc6535ead8f388f86c0fd26b4eb91a920c042696</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>"Rohit Deshmukh"</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>"rohit.deshmukh.54@example.com"</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>"GD4HUQN2HRD7EHUUKSKECNYAAZMBEJCP4WEBUP2E43Y5WJYLTIUJNXA5"</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>"India"</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>On-chain gating works beautifully.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>8c610a7be8dc5813d5f24f063aa8d55d9fadb8472cef91f0fe99d705265c8a90</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>

--- a/docs/user-onboarding-feedback.xlsx
+++ b/docs/user-onboarding-feedback.xlsx
@@ -483,22 +483,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>"Ritu Varma"</t>
+          <t>"""Ritu Varma"""</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>"ritu.varma.0@example.com"</t>
+          <t>"""ritu.varma.0@example.com"""</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>"GC7L4HQXSU5UAGAC3PQK557F2WURNC6BEWK7JCG5MFZIEALAUHFWWSZP"</t>
+          <t>"""GC7L4HQXSU5UAGAC3PQK557F2WURNC6BEWK7JCG5MFZIEALAUHFWWSZP"""</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>"India"</t>
+          <t>"""India"""</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -535,22 +535,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>"Lukas Wagner"</t>
+          <t>"""Lukas Wagner"""</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>"lukas.wagner.1@example.com"</t>
+          <t>"""lukas.wagner.1@example.com"""</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>"GAOXVKR3AW5MNZDR65HS472AGZFDK3Z3TAIXY3MJFZ7MO6STYJ4CGCCI"</t>
+          <t>"""GAOXVKR3AW5MNZDR65HS472AGZFDK3Z3TAIXY3MJFZ7MO6STYJ4CGCCI"""</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>"Europe"</t>
+          <t>"""Europe"""</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -587,22 +587,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>"Daniel Castro"</t>
+          <t>"""Daniel Castro"""</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>"daniel.castro.2@example.com"</t>
+          <t>"""daniel.castro.2@example.com"""</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>"GBGQXAQDQT226DMGY7THGQP3MM5PHA73ZND2QZL7E576EJCFQX3R6NB7"</t>
+          <t>"""GBGQXAQDQT226DMGY7THGQP3MM5PHA73ZND2QZL7E576EJCFQX3R6NB7"""</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>"Philippines"</t>
+          <t>"""Philippines"""</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -639,22 +639,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>"Aarav Gupta"</t>
+          <t>"""Aarav Gupta"""</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>"aarav.gupta.3@example.com"</t>
+          <t>"""aarav.gupta.3@example.com"""</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>"GBBSKIIRT3KLJKODELIRJD2AG65SAK3WMQV7CTRYZAZ4LKWWXRDX2BEX"</t>
+          <t>"""GBBSKIIRT3KLJKODELIRJD2AG65SAK3WMQV7CTRYZAZ4LKWWXRDX2BEX"""</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>"India"</t>
+          <t>"""India"""</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -691,22 +691,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>"Emma Meyer"</t>
+          <t>"""Emma Meyer"""</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>"emma.meyer.4@example.com"</t>
+          <t>"""emma.meyer.4@example.com"""</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>"GBPGDQGTBNM4MKVE3GQ7XPXPO553XY2A3QS4X3EFY5ANNR3RIHGVJKTB"</t>
+          <t>"""GBPGDQGTBNM4MKVE3GQ7XPXPO553XY2A3QS4X3EFY5ANNR3RIHGVJKTB"""</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>"Europe"</t>
+          <t>"""Europe"""</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -743,22 +743,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>"Lourdes Perez"</t>
+          <t>"""Lourdes Perez"""</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>"lourdes.perez.5@example.com"</t>
+          <t>"""lourdes.perez.5@example.com"""</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>"GCXFC2NPSEBTW6S4TDN3USEWT2IRSCPFSHBHLF3DODGMO7ZLUPEOW7LT"</t>
+          <t>"""GCXFC2NPSEBTW6S4TDN3USEWT2IRSCPFSHBHLF3DODGMO7ZLUPEOW7LT"""</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>"Philippines"</t>
+          <t>"""Philippines"""</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -795,22 +795,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>"Vikram Rao"</t>
+          <t>"""Vikram Rao"""</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>"vikram.rao.6@example.com"</t>
+          <t>"""vikram.rao.6@example.com"""</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>"GDOHVBKEAQXFTYBSZPEAQI5ITVEYH56VI4NAZUDUMJAWYW5THSBXZM72"</t>
+          <t>"""GDOHVBKEAQXFTYBSZPEAQI5ITVEYH56VI4NAZUDUMJAWYW5THSBXZM72"""</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>"India"</t>
+          <t>"""India"""</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -847,22 +847,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>"Hans Schmidt"</t>
+          <t>"""Hans Schmidt"""</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>"hans.schmidt.7@example.com"</t>
+          <t>"""hans.schmidt.7@example.com"""</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>"GAUNX6XJKDJYAMUOHEMRZRD7HB4SDPTKP37QOZ7QQEI4WD5JSEBUIQYH"</t>
+          <t>"""GAUNX6XJKDJYAMUOHEMRZRD7HB4SDPTKP37QOZ7QQEI4WD5JSEBUIQYH"""</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>"Europe"</t>
+          <t>"""Europe"""</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -899,22 +899,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>"Lourdes Perez"</t>
+          <t>"""Lourdes Perez"""</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>"lourdes.perez.8@example.com"</t>
+          <t>"""lourdes.perez.8@example.com"""</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>"GALXPD5EIEHTZFXDXSE4YXZKMQPAUCX4HRSQ2I32NNKTMQM2E4UE5UIZ"</t>
+          <t>"""GALXPD5EIEHTZFXDXSE4YXZKMQPAUCX4HRSQ2I32NNKTMQM2E4UE5UIZ"""</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>"Philippines"</t>
+          <t>"""Philippines"""</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -951,22 +951,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>"Kavita Joshi"</t>
+          <t>"""Kavita Joshi"""</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>"kavita.joshi.9@example.com"</t>
+          <t>"""kavita.joshi.9@example.com"""</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>"GCJSWZ4CF2BKYGOBJ5ICSQS7JJD64N5UY2LA7VIB7ADYNLMRJ6XCZ7LX"</t>
+          <t>"""GCJSWZ4CF2BKYGOBJ5ICSQS7JJD64N5UY2LA7VIB7ADYNLMRJ6XCZ7LX"""</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>"India"</t>
+          <t>"""India"""</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1003,22 +1003,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>"Karla Meyer"</t>
+          <t>"""Karla Meyer"""</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>"karla.meyer.10@example.com"</t>
+          <t>"""karla.meyer.10@example.com"""</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>"GD7XNKHYCQNZO5ZQDNOVRWVUH3CRSTVAWQBHIQO3UQTF252SVZNDM2WN"</t>
+          <t>"""GD7XNKHYCQNZO5ZQDNOVRWVUH3CRSTVAWQBHIQO3UQTF252SVZNDM2WN"""</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>"Europe"</t>
+          <t>"""Europe"""</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1055,22 +1055,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>"Lito Ramos"</t>
+          <t>"""Lito Ramos"""</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>"lito.ramos.11@example.com"</t>
+          <t>"""lito.ramos.11@example.com"""</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>"GAAW4INRXSZKMLIKFTOVOC7ZFGRVCDIZA46LW3RB3BVUNMQ7CVM6QVUE"</t>
+          <t>"""GAAW4INRXSZKMLIKFTOVOC7ZFGRVCDIZA46LW3RB3BVUNMQ7CVM6QVUE"""</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>"Philippines"</t>
+          <t>"""Philippines"""</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1107,22 +1107,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>"Arjun Patel"</t>
+          <t>"""Arjun Patel"""</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>"arjun.patel.12@example.com"</t>
+          <t>"""arjun.patel.12@example.com"""</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>"GCD7JKHOOBFJUJGGDUGXQJNEG4UZYYTJH3Z2ZSCGXWMOKPWOQXS3OUWM"</t>
+          <t>"""GCD7JKHOOBFJUJGGDUGXQJNEG4UZYYTJH3Z2ZSCGXWMOKPWOQXS3OUWM"""</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>"India"</t>
+          <t>"""India"""</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1159,22 +1159,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>"Karolin Roth"</t>
+          <t>"""Karolin Roth"""</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>"karolin.roth.13@example.com"</t>
+          <t>"""karolin.roth.13@example.com"""</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>"GDBOATDHYEFNEAIF67C3LQE67WWCFKQKSKPSBZL2LIKQ2HPSG4L6RZ5P"</t>
+          <t>"""GDBOATDHYEFNEAIF67C3LQE67WWCFKQKSKPSBZL2LIKQ2HPSG4L6RZ5P"""</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>"Europe"</t>
+          <t>"""Europe"""</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1211,22 +1211,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>"Maria Santos"</t>
+          <t>"""Maria Santos"""</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>"maria.santos.14@example.com"</t>
+          <t>"""maria.santos.14@example.com"""</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>"GBWTNQKKFP3E464VIHFO5X6GH2WQ7OUSE7N7LS37FWI3ZD5ZLCAZCRHZ"</t>
+          <t>"""GBWTNQKKFP3E464VIHFO5X6GH2WQ7OUSE7N7LS37FWI3ZD5ZLCAZCRHZ"""</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>"Philippines"</t>
+          <t>"""Philippines"""</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1263,22 +1263,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>"Amit Mishra"</t>
+          <t>"""Amit Mishra"""</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>"amit.mishra.15@example.com"</t>
+          <t>"""amit.mishra.15@example.com"""</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>"GCEW5BVEDM6Q2IHAYGUL5FWH247UQE4YRC42RCO26JTUK6ZWFLVGKDNH"</t>
+          <t>"""GCEW5BVEDM6Q2IHAYGUL5FWH247UQE4YRC42RCO26JTUK6ZWFLVGKDNH"""</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>"India"</t>
+          <t>"""India"""</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1315,22 +1315,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>"Emma Schmidt"</t>
+          <t>"""Emma Schmidt"""</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>"emma.schmidt.16@example.com"</t>
+          <t>"""emma.schmidt.16@example.com"""</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>"GBTBJEILCDOBDAVBMNZXQFWP6HACOCJBVWMEM27ZAAA7FWH7ZIV35XSE"</t>
+          <t>"""GBTBJEILCDOBDAVBMNZXQFWP6HACOCJBVWMEM27ZAAA7FWH7ZIV35XSE"""</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>"Europe"</t>
+          <t>"""Europe"""</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1367,22 +1367,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>"Kylie Aquino"</t>
+          <t>"""Kylie Aquino"""</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>"kylie.aquino.17@example.com"</t>
+          <t>"""kylie.aquino.17@example.com"""</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>"GAKEI6NECXOC5VQON7S7TRVCROYVQCR4J55GLMQQG6M534IFYJI7VKK4"</t>
+          <t>"""GAKEI6NECXOC5VQON7S7TRVCROYVQCR4J55GLMQQG6M534IFYJI7VKK4"""</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>"Philippines"</t>
+          <t>"""Philippines"""</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1419,22 +1419,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>"Neha Gupta"</t>
+          <t>"""Neha Gupta"""</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>"neha.gupta.18@example.com"</t>
+          <t>"""neha.gupta.18@example.com"""</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>"GBTNTSYAOED5NW7OYNUPGLASHAXAYNAG6TMBCPBUP53K6ZEF7DVN4BMW"</t>
+          <t>"""GBTNTSYAOED5NW7OYNUPGLASHAXAYNAG6TMBCPBUP53K6ZEF7DVN4BMW"""</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>"India"</t>
+          <t>"""India"""</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1471,22 +1471,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>"Helena Fischer"</t>
+          <t>"""Helena Fischer"""</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>"helena.fischer.19@example.com"</t>
+          <t>"""helena.fischer.19@example.com"""</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>"GBQXWFFNKNZ2T647TTTPXO22GAD2D6SEBNJUY4EYCQIYBIU3YVKE66DW"</t>
+          <t>"""GBQXWFFNKNZ2T647TTTPXO22GAD2D6SEBNJUY4EYCQIYBIU3YVKE66DW"""</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>"Europe"</t>
+          <t>"""Europe"""</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1523,22 +1523,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>"Melchor Cruz"</t>
+          <t>"""Melchor Cruz"""</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>"melchor.cruz.20@example.com"</t>
+          <t>"""melchor.cruz.20@example.com"""</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>"GAG44IDJCAEFZLR6VGO7R2EF5FKNYD3J7SJTE25OYY3FRSTLTOIH64B3"</t>
+          <t>"""GAG44IDJCAEFZLR6VGO7R2EF5FKNYD3J7SJTE25OYY3FRSTLTOIH64B3"""</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>"Philippines"</t>
+          <t>"""Philippines"""</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1575,22 +1575,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>"Rahul Sharma"</t>
+          <t>"""Rahul Sharma"""</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>"rahul.sharma.21@example.com"</t>
+          <t>"""rahul.sharma.21@example.com"""</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>"GAZTUQXQZ7KCCD45N5QPNBLUBSYQFLMDUV2EC3B4M3JNKQIX5KNMJBH2"</t>
+          <t>"""GAZTUQXQZ7KCCD45N5QPNBLUBSYQFLMDUV2EC3B4M3JNKQIX5KNMJBH2"""</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>"India"</t>
+          <t>"""India"""</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1627,22 +1627,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>"Stephan Lange"</t>
+          <t>"""Stephan Lange"""</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>"stephan.lange.22@example.com"</t>
+          <t>"""stephan.lange.22@example.com"""</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>"GCM4YNW3WHQ7L3VZFIIJNIIV2JXW3GMUHFNVEYFMT47VFCWW2UKCPYDD"</t>
+          <t>"""GCM4YNW3WHQ7L3VZFIIJNIIV2JXW3GMUHFNVEYFMT47VFCWW2UKCPYDD"""</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>"Europe"</t>
+          <t>"""Europe"""</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1679,22 +1679,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>"Felipe Mendoza"</t>
+          <t>"""Felipe Mendoza"""</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>"felipe.mendoza.23@example.com"</t>
+          <t>"""felipe.mendoza.23@example.com"""</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>"GAKS6LERI62F6RVZ35EE2Q5NAAJNTNICK62ILU6T7NJTB6OYHAOYIXBH"</t>
+          <t>"""GAKS6LERI62F6RVZ35EE2Q5NAAJNTNICK62ILU6T7NJTB6OYHAOYIXBH"""</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>"Philippines"</t>
+          <t>"""Philippines"""</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1731,22 +1731,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>"Priya Sen"</t>
+          <t>"""Priya Sen"""</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>"priya.sen.24@example.com"</t>
+          <t>"""priya.sen.24@example.com"""</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>"GABOVAUGW7KB7SLQVWUW5OP7UH5KET4QMYA54FOUZLHB74PS5MHH2TY4"</t>
+          <t>"""GABOVAUGW7KB7SLQVWUW5OP7UH5KET4QMYA54FOUZLHB74PS5MHH2TY4"""</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>"India"</t>
+          <t>"""India"""</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1783,22 +1783,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>"Laura Schmitt"</t>
+          <t>"""Laura Schmitt"""</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>"laura.schmitt.25@example.com"</t>
+          <t>"""laura.schmitt.25@example.com"""</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>"GC52YIDTRRJZEPEYVUY5CVOYWRAMEX72PIPAMXLIUURHQ5UCLQCXEGTR"</t>
+          <t>"""GC52YIDTRRJZEPEYVUY5CVOYWRAMEX72PIPAMXLIUURHQ5UCLQCXEGTR"""</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>"Europe"</t>
+          <t>"""Europe"""</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1835,22 +1835,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>"Lourdes Perez"</t>
+          <t>"""Lourdes Perez"""</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>"lourdes.perez.26@example.com"</t>
+          <t>"""lourdes.perez.26@example.com"""</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>"GBLXKW7TDQPYFTVCLVPF3GSHFYBH4T56JAALEIKL2QFPAMFZAMYYKQ2C"</t>
+          <t>"""GBLXKW7TDQPYFTVCLVPF3GSHFYBH4T56JAALEIKL2QFPAMFZAMYYKQ2C"""</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>"Philippines"</t>
+          <t>"""Philippines"""</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1887,22 +1887,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>"Sandeep Patil"</t>
+          <t>"""Sandeep Patil"""</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>"sandeep.patil.27@example.com"</t>
+          <t>"""sandeep.patil.27@example.com"""</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>"GCZTXJKHGXTUCHYGM7RYZRIIX7VIK7JHOCF4XERYKVRVVKG2HNEGTC4P"</t>
+          <t>"""GCZTXJKHGXTUCHYGM7RYZRIIX7VIK7JHOCF4XERYKVRVVKG2HNEGTC4P"""</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>"India"</t>
+          <t>"""India"""</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1939,22 +1939,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>"Hans Weber"</t>
+          <t>"""Hans Weber"""</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>"hans.weber.28@example.com"</t>
+          <t>"""hans.weber.28@example.com"""</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>"GBJMJI2AZWNY2ZJL4NUNECIN6D7VUB3CVCJJZUYBAOKR6UO5QHMZYQ7Z"</t>
+          <t>"""GBJMJI2AZWNY2ZJL4NUNECIN6D7VUB3CVCJJZUYBAOKR6UO5QHMZYQ7Z"""</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>"Europe"</t>
+          <t>"""Europe"""</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1991,22 +1991,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>"Melchor Cruz"</t>
+          <t>"""Melchor Cruz"""</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>"melchor.cruz.29@example.com"</t>
+          <t>"""melchor.cruz.29@example.com"""</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>"GDG6YTCNYRUMWA4RJLIWOQFQ4SZYJGSAR2X7RKIXFMB3ZB6XXD6QDOYC"</t>
+          <t>"""GDG6YTCNYRUMWA4RJLIWOQFQ4SZYJGSAR2X7RKIXFMB3ZB6XXD6QDOYC"""</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>"Philippines"</t>
+          <t>"""Philippines"""</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2043,22 +2043,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>"Rohan Verma"</t>
+          <t>"""Rohan Verma"""</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>"rohan.verma.30@example.com"</t>
+          <t>"""rohan.verma.30@example.com"""</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>"GARDHBXVWSASPYUPSACHUIEYZSXAIE6A2N2QBJCDHXQEY6SV36TV5PXV"</t>
+          <t>"""GARDHBXVWSASPYUPSACHUIEYZSXAIE6A2N2QBJCDHXQEY6SV36TV5PXV"""</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>"India"</t>
+          <t>"""India"""</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2095,22 +2095,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>"Anna Becker"</t>
+          <t>"""Anna Becker"""</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>"anna.becker.31@example.com"</t>
+          <t>"""anna.becker.31@example.com"""</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>"GDOZFUGAHPMZYAOO7PHRFRG6RUDPN2IG4OFKKC6P7YG73SA7HBCE6HAF"</t>
+          <t>"""GDOZFUGAHPMZYAOO7PHRFRG6RUDPN2IG4OFKKC6P7YG73SA7HBCE6HAF"""</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>"Europe"</t>
+          <t>"""Europe"""</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2147,22 +2147,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>"Arnel Santos"</t>
+          <t>"""Arnel Santos"""</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>"arnel.santos.32@example.com"</t>
+          <t>"""arnel.santos.32@example.com"""</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>"GA3KJLOBLKFWOLBY36WTSGEGWD7GQH6TL22LUFUILNCW6RNBNZ5KMP4R"</t>
+          <t>"""GA3KJLOBLKFWOLBY36WTSGEGWD7GQH6TL22LUFUILNCW6RNBNZ5KMP4R"""</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>"Philippines"</t>
+          <t>"""Philippines"""</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2199,22 +2199,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>"Rahul Sharma"</t>
+          <t>"""Rahul Sharma"""</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>"rahul.sharma.33@example.com"</t>
+          <t>"""rahul.sharma.33@example.com"""</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>"GCBLUHLM3JS5E4WUPD67HWG5SZYUOU44GGOE6MXBOMLUYUSWTNCPZP5L"</t>
+          <t>"""GCBLUHLM3JS5E4WUPD67HWG5SZYUOU44GGOE6MXBOMLUYUSWTNCPZP5L"""</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>"India"</t>
+          <t>"""India"""</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2251,22 +2251,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>"Sophia Neumann"</t>
+          <t>"""Sophia Neumann"""</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>"sophia.neumann.34@example.com"</t>
+          <t>"""sophia.neumann.34@example.com"""</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>"GCPHCWRJ34TSFWQCADDITLKRUYWQLGQIPW6XRDQQXKVXIO4MI3P2PAXM"</t>
+          <t>"""GCPHCWRJ34TSFWQCADDITLKRUYWQLGQIPW6XRDQQXKVXIO4MI3P2PAXM"""</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>"Europe"</t>
+          <t>"""Europe"""</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2303,22 +2303,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>"Bernardo Diaz"</t>
+          <t>"""Bernardo Diaz"""</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>"bernardo.diaz.35@example.com"</t>
+          <t>"""bernardo.diaz.35@example.com"""</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>"GDRKEW4YIU7GEWU5NLJCKE5Z22LCRVVXMGFBOTJP3KY6IQQFS5BR6F4J"</t>
+          <t>"""GDRKEW4YIU7GEWU5NLJCKE5Z22LCRVVXMGFBOTJP3KY6IQQFS5BR6F4J"""</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>"Philippines"</t>
+          <t>"""Philippines"""</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2355,22 +2355,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>"Nisha Nair"</t>
+          <t>"""Nisha Nair"""</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>"nisha.nair.36@example.com"</t>
+          <t>"""nisha.nair.36@example.com"""</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>"GBYRMSEGAH3GCMNEHBVBTNA72SA7YAIQWI7LVORB43WN6TNQEU26T7FU"</t>
+          <t>"""GBYRMSEGAH3GCMNEHBVBTNA72SA7YAIQWI7LVORB43WN6TNQEU26T7FU"""</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>"India"</t>
+          <t>"""India"""</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2407,22 +2407,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>"Sabine Hoffmann"</t>
+          <t>"""Sabine Hoffmann"""</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>"sabine.hoffmann.37@example.com"</t>
+          <t>"""sabine.hoffmann.37@example.com"""</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>"GAL2JVH2XVGNNBITMOHJ3FQT4HTLHZ6VI2VREMLXZTNDUKQ4Q356UUDN"</t>
+          <t>"""GAL2JVH2XVGNNBITMOHJ3FQT4HTLHZ6VI2VREMLXZTNDUKQ4Q356UUDN"""</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>"Europe"</t>
+          <t>"""Europe"""</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2459,22 +2459,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>"Lito Ramos"</t>
+          <t>"""Lito Ramos"""</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>"lito.ramos.38@example.com"</t>
+          <t>"""lito.ramos.38@example.com"""</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>"GCLXS4S747TGN2AA6RHBRBLZ2IBYHRVPEZQ6ZU6WFKPZZWBROE55ZETB"</t>
+          <t>"""GCLXS4S747TGN2AA6RHBRBLZ2IBYHRVPEZQ6ZU6WFKPZZWBROE55ZETB"""</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>"Philippines"</t>
+          <t>"""Philippines"""</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2511,22 +2511,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>"Rohan Mehta"</t>
+          <t>"""Rohan Mehta"""</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>"rohan.mehta.39@example.com"</t>
+          <t>"""rohan.mehta.39@example.com"""</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>"GCFEO32K2H2HJSWN45C3EHTJB6PR422MCMX4T4P5ADDUS72YX4UTKDIJ"</t>
+          <t>"""GCFEO32K2H2HJSWN45C3EHTJB6PR422MCMX4T4P5ADDUS72YX4UTKDIJ"""</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>"India"</t>
+          <t>"""India"""</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2563,22 +2563,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>"Karolin Roth"</t>
+          <t>"""Karolin Roth"""</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>"karolin.roth.40@example.com"</t>
+          <t>"""karolin.roth.40@example.com"""</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>"GCKLX3VRMMSEWUCZ5MJ73EYWNMWSNJB5JMYVIBK6CXY5K5PFLOHGQNXQ"</t>
+          <t>"""GCKLX3VRMMSEWUCZ5MJ73EYWNMWSNJB5JMYVIBK6CXY5K5PFLOHGQNXQ"""</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>"Europe"</t>
+          <t>"""Europe"""</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2615,22 +2615,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>"Teresa Aquino"</t>
+          <t>"""Teresa Aquino"""</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>"teresa.aquino.41@example.com"</t>
+          <t>"""teresa.aquino.41@example.com"""</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>"GANJOHRHWQY4JVSMSQ56L6JVW23XVYM3VA243UE2DVCSBMHWGBLEYC6P"</t>
+          <t>"""GANJOHRHWQY4JVSMSQ56L6JVW23XVYM3VA243UE2DVCSBMHWGBLEYC6P"""</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>"Philippines"</t>
+          <t>"""Philippines"""</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2667,22 +2667,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>"Vikram Rao"</t>
+          <t>"""Vikram Rao"""</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>"vikram.rao.42@example.com"</t>
+          <t>"""vikram.rao.42@example.com"""</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>"GAPM4SJGNGWPS22JIQZU67NQRQSDZPVTX3VCMHBNMAIDV5JVL6CV5B3Q"</t>
+          <t>"""GAPM4SJGNGWPS22JIQZU67NQRQSDZPVTX3VCMHBNMAIDV5JVL6CV5B3Q"""</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>"India"</t>
+          <t>"""India"""</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2719,22 +2719,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>"Laura Fischer"</t>
+          <t>"""Laura Fischer"""</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>"laura.fischer.43@example.com"</t>
+          <t>"""laura.fischer.43@example.com"""</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>"GC7RO2TZYW5EVTVFLL45I7NNWHFBAGTL7KUTTWSNHDAHUQBJSM7GXPS7"</t>
+          <t>"""GC7RO2TZYW5EVTVFLL45I7NNWHFBAGTL7KUTTWSNHDAHUQBJSM7GXPS7"""</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>"Europe"</t>
+          <t>"""Europe"""</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2771,22 +2771,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>"Gloria Macapagal"</t>
+          <t>"""Gloria Macapagal"""</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>"gloria.macapagal.44@example.com"</t>
+          <t>"""gloria.macapagal.44@example.com"""</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>"GBDCNRVJOT3SP6SLFDCNQYEYP5BTXFMFD6GDODAXPCKBDHEIG7Z4466C"</t>
+          <t>"""GBDCNRVJOT3SP6SLFDCNQYEYP5BTXFMFD6GDODAXPCKBDHEIG7Z4466C"""</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>"Philippines"</t>
+          <t>"""Philippines"""</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2823,22 +2823,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>"Ritu Varma"</t>
+          <t>"""Ritu Varma"""</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>"ritu.varma.45@example.com"</t>
+          <t>"""ritu.varma.45@example.com"""</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>"GAZXRVJ3DNTJNT6BMU57N63YKKSZVOPL3CPM7WIPUVCMEJP3QPFTTU3Q"</t>
+          <t>"""GAZXRVJ3DNTJNT6BMU57N63YKKSZVOPL3CPM7WIPUVCMEJP3QPFTTU3Q"""</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>"India"</t>
+          <t>"""India"""</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2875,22 +2875,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>"Wolfgang Becker"</t>
+          <t>"""Wolfgang Becker"""</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>"wolfgang.becker.46@example.com"</t>
+          <t>"""wolfgang.becker.46@example.com"""</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>"GB4CPN2TFXGHS76MTP63ACAYAZU2WBS4EEDMW4SSY6IRD5KLANDIMMRT"</t>
+          <t>"""GB4CPN2TFXGHS76MTP63ACAYAZU2WBS4EEDMW4SSY6IRD5KLANDIMMRT"""</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>"Europe"</t>
+          <t>"""Europe"""</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2927,22 +2927,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>"Arnel Santos"</t>
+          <t>"""Arnel Santos"""</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>"arnel.santos.47@example.com"</t>
+          <t>"""arnel.santos.47@example.com"""</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>"GBGF56HKJPIIZ4S6B575PN4MZICWSHPI7A2GMVCIGDHWNHFDL6RSAZUE"</t>
+          <t>"""GBGF56HKJPIIZ4S6B575PN4MZICWSHPI7A2GMVCIGDHWNHFDL6RSAZUE"""</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>"Philippines"</t>
+          <t>"""Philippines"""</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2979,22 +2979,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>"Vikram Rao"</t>
+          <t>"""Vikram Rao"""</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>"vikram.rao.48@example.com"</t>
+          <t>"""vikram.rao.48@example.com"""</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>"GD5XF5CBJXLJ4VTGYBNNVLKCJW455JPUPOEOXMUUNQCO4S4FLVXSDRP4"</t>
+          <t>"""GD5XF5CBJXLJ4VTGYBNNVLKCJW455JPUPOEOXMUUNQCO4S4FLVXSDRP4"""</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>"India"</t>
+          <t>"""India"""</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3031,22 +3031,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>"Pierre Dubois"</t>
+          <t>"""Pierre Dubois"""</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>"pierre.dubois.49@example.com"</t>
+          <t>"""pierre.dubois.49@example.com"""</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>"GB7XG4NKWH3L37IYXH55V6GVQIEO6UT3T3YUVY7QNM3GXKPOQ66JPQ7F"</t>
+          <t>"""GB7XG4NKWH3L37IYXH55V6GVQIEO6UT3T3YUVY7QNM3GXKPOQ66JPQ7F"""</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>"Europe"</t>
+          <t>"""Europe"""</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3083,22 +3083,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>"Melchor Cruz"</t>
+          <t>"""Melchor Cruz"""</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>"melchor.cruz.50@example.com"</t>
+          <t>"""melchor.cruz.50@example.com"""</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>"GCIRUKHIYTZSXNG5XWKJC5TS5N2WF6B5ETIBT6D6AAN2L5FYGJC4J3CO"</t>
+          <t>"""GCIRUKHIYTZSXNG5XWKJC5TS5N2WF6B5ETIBT6D6AAN2L5FYGJC4J3CO"""</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>"Philippines"</t>
+          <t>"""Philippines"""</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3135,22 +3135,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>"Sandeep Patil"</t>
+          <t>"""Sandeep Patil"""</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>"sandeep.patil.51@example.com"</t>
+          <t>"""sandeep.patil.51@example.com"""</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>"GCCAIYMFBLFQE7QBD4BQT75TEJBPN5RVFKRBCCYRFNIO2QLLIAV646WM"</t>
+          <t>"""GCCAIYMFBLFQE7QBD4BQT75TEJBPN5RVFKRBCCYRFNIO2QLLIAV646WM"""</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>"India"</t>
+          <t>"""India"""</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3187,22 +3187,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>"Emma Meyer"</t>
+          <t>"""Emma Meyer"""</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>"emma.meyer.52@example.com"</t>
+          <t>"""emma.meyer.52@example.com"""</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>"GBNJELTJYTHIW56XQMVPFIYUZU3VCSMYBPNGR3JS76I5G4MMBJLYWUJT"</t>
+          <t>"""GBNJELTJYTHIW56XQMVPFIYUZU3VCSMYBPNGR3JS76I5G4MMBJLYWUJT"""</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>"Europe"</t>
+          <t>"""Europe"""</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3239,22 +3239,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>"Eduardo Reyes"</t>
+          <t>"""Eduardo Reyes"""</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>"eduardo.reyes.53@example.com"</t>
+          <t>"""eduardo.reyes.53@example.com"""</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>"GDUSSRTUBIJ3RFMPQE3UPTGU3LWUQBQQH3PYVHZIAAA4QPOJOW5S5TMZ"</t>
+          <t>"""GDUSSRTUBIJ3RFMPQE3UPTGU3LWUQBQQH3PYVHZIAAA4QPOJOW5S5TMZ"""</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>"Philippines"</t>
+          <t>"""Philippines"""</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3291,22 +3291,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>"Rohit Deshmukh"</t>
+          <t>"""Rohit Deshmukh"""</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>"rohit.deshmukh.54@example.com"</t>
+          <t>"""rohit.deshmukh.54@example.com"""</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>"GD4HUQN2HRD7EHUUKSKECNYAAZMBEJCP4WEBUP2E43Y5WJYLTIUJNXA5"</t>
+          <t>"""GD4HUQN2HRD7EHUUKSKECNYAAZMBEJCP4WEBUP2E43Y5WJYLTIUJNXA5"""</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>"India"</t>
+          <t>"""India"""</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
